--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15EA4AD9-8D7C-4506-8634-9DE435AD4465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8405377-2B11-4355-8E26-C7F598E70B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -244,23 +244,23 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -285,6 +285,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="REQUERIMIENTO COMPRAS"/>
@@ -337,35 +338,35 @@
         </row>
         <row r="9">
           <cell r="B9">
-            <v>163855.10728794136</v>
+            <v>200219.36641545361</v>
           </cell>
           <cell r="C9">
             <v>13781.46783678359</v>
           </cell>
           <cell r="D9">
-            <v>11.889525065726449</v>
+            <v>14.52815975676087</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>282371.5244729534</v>
+            <v>276684.66543270595</v>
           </cell>
           <cell r="C10">
             <v>3833.3433721023121</v>
           </cell>
           <cell r="D10">
-            <v>73.66194391244764</v>
+            <v>72.178419352233604</v>
           </cell>
         </row>
         <row r="14">
           <cell r="B14">
-            <v>136571.55674831438</v>
+            <v>194311.40674831436</v>
           </cell>
           <cell r="C14">
             <v>572841.76700551296</v>
           </cell>
           <cell r="D14">
-            <v>0.23841061286824786</v>
+            <v>0.33920607389377794</v>
           </cell>
         </row>
         <row r="15">
@@ -400,65 +401,65 @@
         </row>
         <row r="24">
           <cell r="B24">
-            <v>163855.10728794136</v>
+            <v>200219.36641545361</v>
           </cell>
           <cell r="C24">
-            <v>446226.63176089479</v>
+            <v>476904.03184815956</v>
           </cell>
           <cell r="D24">
-            <v>0.36720154205350336</v>
+            <v>0.41983156577548292</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25">
-            <v>282371.5244729534</v>
+            <v>276684.66543270595</v>
           </cell>
           <cell r="D25">
-            <v>0.63279845794649658</v>
+            <v>0.58016843422451703</v>
           </cell>
         </row>
         <row r="29">
           <cell r="B29">
-            <v>11.889525065726449</v>
+            <v>14.52815975676087</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>1.8895250657264491</v>
+            <v>4.5281597567608696</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30">
-            <v>73.66194391244764</v>
+            <v>72.178419352233604</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>58.66194391244764</v>
+            <v>57.178419352233604</v>
           </cell>
         </row>
         <row r="34">
           <cell r="B34">
-            <v>163855.10728794136</v>
+            <v>200219.36641545361</v>
           </cell>
           <cell r="C34">
-            <v>136571.55674831438</v>
+            <v>194311.40674831436</v>
           </cell>
           <cell r="D34">
-            <v>123487.42222840591</v>
+            <v>144955.94980589359</v>
           </cell>
         </row>
         <row r="35">
           <cell r="B35">
-            <v>282371.5244729534</v>
+            <v>276684.66543270595</v>
           </cell>
           <cell r="C35">
             <v>4527.1099999999997</v>
           </cell>
           <cell r="D35">
-            <v>63563.649499363841</v>
+            <v>68680.560124462223</v>
           </cell>
         </row>
       </sheetData>
@@ -793,20 +794,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -823,46 +824,46 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B4</f>
         <v>150253.06764921901</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C4</f>
         <v>13781.46783678359</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D4</f>
         <v>10.902544593122677</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B5</f>
         <v>349539.95608949504</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C5</f>
         <v>3833.3433721023121</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D5</f>
         <v>91.184097577409986</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -879,46 +880,46 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>163855.10728794136</v>
-      </c>
-      <c r="C9" s="4">
+        <v>200219.36641545361</v>
+      </c>
+      <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
         <v>13781.46783678359</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>11.889525065726449</v>
+        <v>14.52815975676087</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>282371.5244729534</v>
-      </c>
-      <c r="C10" s="4">
+        <v>276684.66543270595</v>
+      </c>
+      <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
         <v>3833.3433721023121</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>73.66194391244764</v>
+        <v>72.178419352233604</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -935,46 +936,46 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B14</f>
-        <v>136571.55674831438</v>
-      </c>
-      <c r="C14" s="4">
+        <v>194311.40674831436</v>
+      </c>
+      <c r="C14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C14</f>
         <v>572841.76700551296</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D14</f>
-        <v>0.23841061286824786</v>
+        <v>0.33920607389377794</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B15</f>
         <v>4527.1099999999997</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C15</f>
         <v>88362.038183632205</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D15</f>
         <v>5.1233652969749868E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -991,43 +992,43 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B19</f>
         <v>150253.06764921901</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C19</f>
         <v>499793.02373871405</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D19</f>
         <v>0.30063058208625487</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B20</f>
         <v>349539.95608949504</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="6">
+      <c r="C20" s="9"/>
+      <c r="D20" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D20</f>
         <v>0.69936941791374507</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
@@ -1044,49 +1045,49 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>163855.10728794136</v>
-      </c>
-      <c r="C24" s="7">
+        <v>200219.36641545361</v>
+      </c>
+      <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>446226.63176089479</v>
-      </c>
-      <c r="D24" s="6">
+        <v>476904.03184815956</v>
+      </c>
+      <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.36720154205350336</v>
+        <v>0.41983156577548292</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>282371.5244729534</v>
-      </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="6">
+        <v>276684.66543270595</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.63279845794649658</v>
+        <v>0.58016843422451703</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>2</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C28" t="s">
@@ -1097,46 +1098,46 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>11.889525065726449</v>
-      </c>
-      <c r="C29" s="10">
+        <v>14.52815975676087</v>
+      </c>
+      <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
         <v>10</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>1.8895250657264491</v>
+        <v>4.5281597567608696</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>73.66194391244764</v>
-      </c>
-      <c r="C30" s="10">
+        <v>72.178419352233604</v>
+      </c>
+      <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
         <v>15</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>58.66194391244764</v>
+        <v>57.178419352233604</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
@@ -1153,37 +1154,37 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>163855.10728794136</v>
-      </c>
-      <c r="C34" s="4">
+        <v>200219.36641545361</v>
+      </c>
+      <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
-        <v>136571.55674831438</v>
-      </c>
-      <c r="D34" s="4">
+        <v>194311.40674831436</v>
+      </c>
+      <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>123487.42222840591</v>
+        <v>144955.94980589359</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>282371.5244729534</v>
-      </c>
-      <c r="C35" s="4">
+        <v>276684.66543270595</v>
+      </c>
+      <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
         <v>4527.1099999999997</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>63563.649499363841</v>
+        <v>68680.560124462223</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8405377-2B11-4355-8E26-C7F598E70B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58574392-7A38-4E8A-9EE5-89343F211D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58574392-7A38-4E8A-9EE5-89343F211D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FD7F15-2AC6-4F9A-9796-81C0AD061BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -338,24 +338,24 @@
         </row>
         <row r="9">
           <cell r="B9">
-            <v>200219.36641545361</v>
+            <v>179101.51877194631</v>
           </cell>
           <cell r="C9">
             <v>13781.46783678359</v>
           </cell>
           <cell r="D9">
-            <v>14.52815975676087</v>
+            <v>12.995823151283878</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>276684.66543270595</v>
+            <v>266962.84207953367</v>
           </cell>
           <cell r="C10">
             <v>3833.3433721023121</v>
           </cell>
           <cell r="D10">
-            <v>72.178419352233604</v>
+            <v>69.642298162589029</v>
           </cell>
         </row>
         <row r="14">
@@ -401,65 +401,65 @@
         </row>
         <row r="24">
           <cell r="B24">
-            <v>200219.36641545361</v>
+            <v>179101.51877194631</v>
           </cell>
           <cell r="C24">
-            <v>476904.03184815956</v>
+            <v>446064.36085147999</v>
           </cell>
           <cell r="D24">
-            <v>0.41983156577548292</v>
+            <v>0.40151497068733388</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25">
-            <v>276684.66543270595</v>
+            <v>266962.84207953367</v>
           </cell>
           <cell r="D25">
-            <v>0.58016843422451703</v>
+            <v>0.59848502931266612</v>
           </cell>
         </row>
         <row r="29">
           <cell r="B29">
-            <v>14.52815975676087</v>
+            <v>12.995823151283878</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>4.5281597567608696</v>
+            <v>2.9958231512838776</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30">
-            <v>72.178419352233604</v>
+            <v>69.642298162589029</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>57.178419352233604</v>
+            <v>54.642298162589029</v>
           </cell>
         </row>
         <row r="34">
           <cell r="B34">
-            <v>200219.36641545361</v>
+            <v>179101.51877194631</v>
           </cell>
           <cell r="C34">
             <v>194311.40674831436</v>
           </cell>
           <cell r="D34">
-            <v>144955.94980589359</v>
+            <v>167516.03153571667</v>
           </cell>
         </row>
         <row r="35">
           <cell r="B35">
-            <v>276684.66543270595</v>
+            <v>266962.84207953367</v>
           </cell>
           <cell r="C35">
             <v>4527.1099999999997</v>
           </cell>
           <cell r="D35">
-            <v>68680.560124462223</v>
+            <v>82113.842168804462</v>
           </cell>
         </row>
       </sheetData>
@@ -885,7 +885,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>200219.36641545361</v>
+        <v>179101.51877194631</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -893,7 +893,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>14.52815975676087</v>
+        <v>12.995823151283878</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -902,7 +902,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>276684.66543270595</v>
+        <v>266962.84207953367</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -910,7 +910,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>72.178419352233604</v>
+        <v>69.642298162589029</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1050,15 +1050,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>200219.36641545361</v>
+        <v>179101.51877194631</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>476904.03184815956</v>
+        <v>446064.36085147999</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.41983156577548292</v>
+        <v>0.40151497068733388</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>276684.66543270595</v>
+        <v>266962.84207953367</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.58016843422451703</v>
+        <v>0.59848502931266612</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>14.52815975676087</v>
+        <v>12.995823151283878</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>4.5281597567608696</v>
+        <v>2.9958231512838776</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>72.178419352233604</v>
+        <v>69.642298162589029</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>57.178419352233604</v>
+        <v>54.642298162589029</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>200219.36641545361</v>
+        <v>179101.51877194631</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>144955.94980589359</v>
+        <v>167516.03153571667</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>276684.66543270595</v>
+        <v>266962.84207953367</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>68680.560124462223</v>
+        <v>82113.842168804462</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FD7F15-2AC6-4F9A-9796-81C0AD061BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FCCB3E-B5B4-4F36-8777-AB98D0663486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -338,24 +338,24 @@
         </row>
         <row r="9">
           <cell r="B9">
-            <v>179101.51877194631</v>
+            <v>177603.1332655861</v>
           </cell>
           <cell r="C9">
             <v>13781.46783678359</v>
           </cell>
           <cell r="D9">
-            <v>12.995823151283878</v>
+            <v>12.887098483918553</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>266962.84207953367</v>
+            <v>264653.60524032428</v>
           </cell>
           <cell r="C10">
             <v>3833.3433721023121</v>
           </cell>
           <cell r="D10">
-            <v>69.642298162589029</v>
+            <v>69.039890129952241</v>
           </cell>
         </row>
         <row r="14">
@@ -401,65 +401,65 @@
         </row>
         <row r="24">
           <cell r="B24">
-            <v>179101.51877194631</v>
+            <v>177603.1332655861</v>
           </cell>
           <cell r="C24">
-            <v>446064.36085147999</v>
+            <v>442256.73850591038</v>
           </cell>
           <cell r="D24">
-            <v>0.40151497068733388</v>
+            <v>0.40158378109870813</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25">
-            <v>266962.84207953367</v>
+            <v>264653.60524032428</v>
           </cell>
           <cell r="D25">
-            <v>0.59848502931266612</v>
+            <v>0.59841621890129193</v>
           </cell>
         </row>
         <row r="29">
           <cell r="B29">
-            <v>12.995823151283878</v>
+            <v>12.887098483918553</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>2.9958231512838776</v>
+            <v>2.8870984839185532</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30">
-            <v>69.642298162589029</v>
+            <v>69.039890129952241</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>54.642298162589029</v>
+            <v>54.039890129952241</v>
           </cell>
         </row>
         <row r="34">
           <cell r="B34">
-            <v>179101.51877194631</v>
+            <v>177603.1332655861</v>
           </cell>
           <cell r="C34">
             <v>194311.40674831436</v>
           </cell>
           <cell r="D34">
-            <v>167516.03153571667</v>
+            <v>179763.28685786645</v>
           </cell>
         </row>
         <row r="35">
           <cell r="B35">
-            <v>266962.84207953367</v>
+            <v>264653.60524032428</v>
           </cell>
           <cell r="C35">
             <v>4527.1099999999997</v>
           </cell>
           <cell r="D35">
-            <v>82113.842168804462</v>
+            <v>86382.614781092998</v>
           </cell>
         </row>
       </sheetData>
@@ -885,7 +885,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>179101.51877194631</v>
+        <v>177603.1332655861</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -893,7 +893,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>12.995823151283878</v>
+        <v>12.887098483918553</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -902,7 +902,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>266962.84207953367</v>
+        <v>264653.60524032428</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -910,7 +910,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>69.642298162589029</v>
+        <v>69.039890129952241</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1050,15 +1050,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>179101.51877194631</v>
+        <v>177603.1332655861</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>446064.36085147999</v>
+        <v>442256.73850591038</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.40151497068733388</v>
+        <v>0.40158378109870813</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>266962.84207953367</v>
+        <v>264653.60524032428</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.59848502931266612</v>
+        <v>0.59841621890129193</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>12.995823151283878</v>
+        <v>12.887098483918553</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>2.9958231512838776</v>
+        <v>2.8870984839185532</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>69.642298162589029</v>
+        <v>69.039890129952241</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>54.642298162589029</v>
+        <v>54.039890129952241</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>179101.51877194631</v>
+        <v>177603.1332655861</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>167516.03153571667</v>
+        <v>179763.28685786645</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>266962.84207953367</v>
+        <v>264653.60524032428</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>82113.842168804462</v>
+        <v>86382.614781092998</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FCCB3E-B5B4-4F36-8777-AB98D0663486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B24095-E392-419A-AFE4-9243880298E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -338,46 +338,46 @@
         </row>
         <row r="9">
           <cell r="B9">
-            <v>177603.1332655861</v>
+            <v>160068.50721729058</v>
           </cell>
           <cell r="C9">
             <v>13781.46783678359</v>
           </cell>
           <cell r="D9">
-            <v>12.887098483918553</v>
+            <v>11.614764777816905</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>264653.60524032428</v>
+            <v>269664.14633368974</v>
           </cell>
           <cell r="C10">
             <v>3833.3433721023121</v>
           </cell>
           <cell r="D10">
-            <v>69.039890129952241</v>
+            <v>70.346984383451783</v>
           </cell>
         </row>
         <row r="14">
           <cell r="B14">
-            <v>194311.40674831436</v>
+            <v>194423.00674831436</v>
           </cell>
           <cell r="C14">
             <v>572841.76700551296</v>
           </cell>
           <cell r="D14">
-            <v>0.33920607389377794</v>
+            <v>0.33940089209040386</v>
           </cell>
         </row>
         <row r="15">
           <cell r="B15">
-            <v>4527.1099999999997</v>
+            <v>9290.8632288118097</v>
           </cell>
           <cell r="C15">
             <v>88362.038183632205</v>
           </cell>
           <cell r="D15">
-            <v>5.1233652969749868E-2</v>
+            <v>0.10514541560826976</v>
           </cell>
         </row>
         <row r="19">
@@ -401,65 +401,65 @@
         </row>
         <row r="24">
           <cell r="B24">
-            <v>177603.1332655861</v>
+            <v>160068.50721729058</v>
           </cell>
           <cell r="C24">
-            <v>442256.73850591038</v>
+            <v>429732.65355098032</v>
           </cell>
           <cell r="D24">
-            <v>0.40158378109870813</v>
+            <v>0.37248392900704069</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25">
-            <v>264653.60524032428</v>
+            <v>269664.14633368974</v>
           </cell>
           <cell r="D25">
-            <v>0.59841621890129193</v>
+            <v>0.62751607099295925</v>
           </cell>
         </row>
         <row r="29">
           <cell r="B29">
-            <v>12.887098483918553</v>
+            <v>11.614764777816905</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>2.8870984839185532</v>
+            <v>1.6147647778169052</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30">
-            <v>69.039890129952241</v>
+            <v>70.346984383451783</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>54.039890129952241</v>
+            <v>55.346984383451783</v>
           </cell>
         </row>
         <row r="34">
           <cell r="B34">
-            <v>177603.1332655861</v>
+            <v>160068.50721729058</v>
           </cell>
           <cell r="C34">
-            <v>194311.40674831436</v>
+            <v>194423.00674831436</v>
           </cell>
           <cell r="D34">
-            <v>179763.28685786645</v>
+            <v>199004.30517458299</v>
           </cell>
         </row>
         <row r="35">
           <cell r="B35">
-            <v>264653.60524032428</v>
+            <v>269664.14633368974</v>
           </cell>
           <cell r="C35">
-            <v>4527.1099999999997</v>
+            <v>9290.8632288118097</v>
           </cell>
           <cell r="D35">
-            <v>86382.614781092998</v>
+            <v>94614.110383616455</v>
           </cell>
         </row>
       </sheetData>
@@ -885,7 +885,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>177603.1332655861</v>
+        <v>160068.50721729058</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -893,7 +893,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>12.887098483918553</v>
+        <v>11.614764777816905</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -902,7 +902,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>264653.60524032428</v>
+        <v>269664.14633368974</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -910,7 +910,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>69.039890129952241</v>
+        <v>70.346984383451783</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -941,7 +941,7 @@
       </c>
       <c r="B14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B14</f>
-        <v>194311.40674831436</v>
+        <v>194423.00674831436</v>
       </c>
       <c r="C14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C14</f>
@@ -949,7 +949,7 @@
       </c>
       <c r="D14" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D14</f>
-        <v>0.33920607389377794</v>
+        <v>0.33940089209040386</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -958,7 +958,7 @@
       </c>
       <c r="B15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B15</f>
-        <v>4527.1099999999997</v>
+        <v>9290.8632288118097</v>
       </c>
       <c r="C15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C15</f>
@@ -966,7 +966,7 @@
       </c>
       <c r="D15" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D15</f>
-        <v>5.1233652969749868E-2</v>
+        <v>0.10514541560826976</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1050,15 +1050,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>177603.1332655861</v>
+        <v>160068.50721729058</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>442256.73850591038</v>
+        <v>429732.65355098032</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.40158378109870813</v>
+        <v>0.37248392900704069</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>264653.60524032428</v>
+        <v>269664.14633368974</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.59841621890129193</v>
+        <v>0.62751607099295925</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>12.887098483918553</v>
+        <v>11.614764777816905</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>2.8870984839185532</v>
+        <v>1.6147647778169052</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>69.039890129952241</v>
+        <v>70.346984383451783</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>54.039890129952241</v>
+        <v>55.346984383451783</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1159,15 +1159,15 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>177603.1332655861</v>
+        <v>160068.50721729058</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
-        <v>194311.40674831436</v>
+        <v>194423.00674831436</v>
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>179763.28685786645</v>
+        <v>199004.30517458299</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1176,15 +1176,15 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>264653.60524032428</v>
+        <v>269664.14633368974</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
-        <v>4527.1099999999997</v>
+        <v>9290.8632288118097</v>
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>86382.614781092998</v>
+        <v>94614.110383616455</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B24095-E392-419A-AFE4-9243880298E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78328E98-EA35-4313-9A46-724A81BA6447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -338,24 +338,24 @@
         </row>
         <row r="9">
           <cell r="B9">
-            <v>160068.50721729058</v>
+            <v>242358.19263423263</v>
           </cell>
           <cell r="C9">
             <v>13781.46783678359</v>
           </cell>
           <cell r="D9">
-            <v>11.614764777816905</v>
+            <v>17.585804030784271</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>269664.14633368974</v>
+            <v>320205.97566983633</v>
           </cell>
           <cell r="C10">
             <v>3833.3433721023121</v>
           </cell>
           <cell r="D10">
-            <v>70.346984383451783</v>
+            <v>83.531774899211925</v>
           </cell>
         </row>
         <row r="14">
@@ -401,65 +401,65 @@
         </row>
         <row r="24">
           <cell r="B24">
-            <v>160068.50721729058</v>
+            <v>242358.19263423263</v>
           </cell>
           <cell r="C24">
-            <v>429732.65355098032</v>
+            <v>562564.16830406897</v>
           </cell>
           <cell r="D24">
-            <v>0.37248392900704069</v>
+            <v>0.43080986363716772</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25">
-            <v>269664.14633368974</v>
+            <v>320205.97566983633</v>
           </cell>
           <cell r="D25">
-            <v>0.62751607099295925</v>
+            <v>0.56919013636283222</v>
           </cell>
         </row>
         <row r="29">
           <cell r="B29">
-            <v>11.614764777816905</v>
+            <v>17.585804030784271</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>1.6147647778169052</v>
+            <v>7.5858040307842707</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30">
-            <v>70.346984383451783</v>
+            <v>83.531774899211925</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>55.346984383451783</v>
+            <v>68.531774899211925</v>
           </cell>
         </row>
         <row r="34">
           <cell r="B34">
-            <v>160068.50721729058</v>
+            <v>242358.19263423263</v>
           </cell>
           <cell r="C34">
             <v>194423.00674831436</v>
           </cell>
           <cell r="D34">
-            <v>199004.30517458299</v>
+            <v>216049.47443858298</v>
           </cell>
         </row>
         <row r="35">
           <cell r="B35">
-            <v>269664.14633368974</v>
+            <v>320205.97566983633</v>
           </cell>
           <cell r="C35">
             <v>9290.8632288118097</v>
           </cell>
           <cell r="D35">
-            <v>94614.110383616455</v>
+            <v>104956.94180147693</v>
           </cell>
         </row>
       </sheetData>
@@ -885,7 +885,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>160068.50721729058</v>
+        <v>242358.19263423263</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -893,7 +893,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>11.614764777816905</v>
+        <v>17.585804030784271</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -902,7 +902,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>269664.14633368974</v>
+        <v>320205.97566983633</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -910,7 +910,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>70.346984383451783</v>
+        <v>83.531774899211925</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1050,15 +1050,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>160068.50721729058</v>
+        <v>242358.19263423263</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>429732.65355098032</v>
+        <v>562564.16830406897</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.37248392900704069</v>
+        <v>0.43080986363716772</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>269664.14633368974</v>
+        <v>320205.97566983633</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.62751607099295925</v>
+        <v>0.56919013636283222</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>11.614764777816905</v>
+        <v>17.585804030784271</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>1.6147647778169052</v>
+        <v>7.5858040307842707</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>70.346984383451783</v>
+        <v>83.531774899211925</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>55.346984383451783</v>
+        <v>68.531774899211925</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>160068.50721729058</v>
+        <v>242358.19263423263</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>199004.30517458299</v>
+        <v>216049.47443858298</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>269664.14633368974</v>
+        <v>320205.97566983633</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>94614.110383616455</v>
+        <v>104956.94180147693</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78328E98-EA35-4313-9A46-724A81BA6447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B03F5E9-E0E2-45B6-8E5D-931BBE95F7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -338,46 +338,46 @@
         </row>
         <row r="9">
           <cell r="B9">
-            <v>242358.19263423263</v>
+            <v>273914.7186931668</v>
           </cell>
           <cell r="C9">
             <v>13781.46783678359</v>
           </cell>
           <cell r="D9">
-            <v>17.585804030784271</v>
+            <v>19.875583786661061</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>320205.97566983633</v>
+            <v>326625.68646658427</v>
           </cell>
           <cell r="C10">
             <v>3833.3433721023121</v>
           </cell>
           <cell r="D10">
-            <v>83.531774899211925</v>
+            <v>85.206477677853755</v>
           </cell>
         </row>
         <row r="14">
           <cell r="B14">
-            <v>194423.00674831436</v>
+            <v>243735.50674831436</v>
           </cell>
           <cell r="C14">
             <v>572841.76700551296</v>
           </cell>
           <cell r="D14">
-            <v>0.33940089209040386</v>
+            <v>0.42548487346239311</v>
           </cell>
         </row>
         <row r="15">
           <cell r="B15">
-            <v>9290.8632288118097</v>
+            <v>19504.496894714972</v>
           </cell>
           <cell r="C15">
             <v>88362.038183632205</v>
           </cell>
           <cell r="D15">
-            <v>0.10514541560826976</v>
+            <v>0.22073389541084509</v>
           </cell>
         </row>
         <row r="19">
@@ -401,65 +401,65 @@
         </row>
         <row r="24">
           <cell r="B24">
-            <v>242358.19263423263</v>
+            <v>273914.7186931668</v>
           </cell>
           <cell r="C24">
-            <v>562564.16830406897</v>
+            <v>600540.40515975107</v>
           </cell>
           <cell r="D24">
-            <v>0.43080986363716772</v>
+            <v>0.45611372080834783</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25">
-            <v>320205.97566983633</v>
+            <v>326625.68646658427</v>
           </cell>
           <cell r="D25">
-            <v>0.56919013636283222</v>
+            <v>0.54388627919165211</v>
           </cell>
         </row>
         <row r="29">
           <cell r="B29">
-            <v>17.585804030784271</v>
+            <v>19.875583786661061</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>7.5858040307842707</v>
+            <v>9.8755837866610605</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30">
-            <v>83.531774899211925</v>
+            <v>85.206477677853755</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>68.531774899211925</v>
+            <v>70.206477677853755</v>
           </cell>
         </row>
         <row r="34">
           <cell r="B34">
-            <v>242358.19263423263</v>
+            <v>273914.7186931668</v>
           </cell>
           <cell r="C34">
-            <v>194423.00674831436</v>
+            <v>243735.50674831436</v>
           </cell>
           <cell r="D34">
-            <v>216049.47443858298</v>
+            <v>235464.38419412248</v>
           </cell>
         </row>
         <row r="35">
           <cell r="B35">
-            <v>320205.97566983633</v>
+            <v>326625.68646658427</v>
           </cell>
           <cell r="C35">
-            <v>9290.8632288118097</v>
+            <v>19504.496894714972</v>
           </cell>
           <cell r="D35">
-            <v>104956.94180147693</v>
+            <v>115442.23722641317</v>
           </cell>
         </row>
       </sheetData>
@@ -885,7 +885,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>242358.19263423263</v>
+        <v>273914.7186931668</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -893,7 +893,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>17.585804030784271</v>
+        <v>19.875583786661061</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -902,7 +902,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>320205.97566983633</v>
+        <v>326625.68646658427</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -910,7 +910,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>83.531774899211925</v>
+        <v>85.206477677853755</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -941,7 +941,7 @@
       </c>
       <c r="B14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B14</f>
-        <v>194423.00674831436</v>
+        <v>243735.50674831436</v>
       </c>
       <c r="C14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C14</f>
@@ -949,7 +949,7 @@
       </c>
       <c r="D14" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D14</f>
-        <v>0.33940089209040386</v>
+        <v>0.42548487346239311</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -958,7 +958,7 @@
       </c>
       <c r="B15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B15</f>
-        <v>9290.8632288118097</v>
+        <v>19504.496894714972</v>
       </c>
       <c r="C15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C15</f>
@@ -966,7 +966,7 @@
       </c>
       <c r="D15" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D15</f>
-        <v>0.10514541560826976</v>
+        <v>0.22073389541084509</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1050,15 +1050,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>242358.19263423263</v>
+        <v>273914.7186931668</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>562564.16830406897</v>
+        <v>600540.40515975107</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.43080986363716772</v>
+        <v>0.45611372080834783</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>320205.97566983633</v>
+        <v>326625.68646658427</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.56919013636283222</v>
+        <v>0.54388627919165211</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>17.585804030784271</v>
+        <v>19.875583786661061</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>7.5858040307842707</v>
+        <v>9.8755837866610605</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>83.531774899211925</v>
+        <v>85.206477677853755</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>68.531774899211925</v>
+        <v>70.206477677853755</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1159,15 +1159,15 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>242358.19263423263</v>
+        <v>273914.7186931668</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
-        <v>194423.00674831436</v>
+        <v>243735.50674831436</v>
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>216049.47443858298</v>
+        <v>235464.38419412248</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1176,15 +1176,15 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>320205.97566983633</v>
+        <v>326625.68646658427</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
-        <v>9290.8632288118097</v>
+        <v>19504.496894714972</v>
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>104956.94180147693</v>
+        <v>115442.23722641317</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B03F5E9-E0E2-45B6-8E5D-931BBE95F7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF2044F-D960-4004-B0EE-5709A34AF761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -338,35 +338,35 @@
         </row>
         <row r="9">
           <cell r="B9">
-            <v>273914.7186931668</v>
+            <v>196969.34364119239</v>
           </cell>
           <cell r="C9">
             <v>13781.46783678359</v>
           </cell>
           <cell r="D9">
-            <v>19.875583786661061</v>
+            <v>14.292334167443981</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>326625.68646658427</v>
+            <v>310867.60124087968</v>
           </cell>
           <cell r="C10">
             <v>3833.3433721023121</v>
           </cell>
           <cell r="D10">
-            <v>85.206477677853755</v>
+            <v>81.095683601751347</v>
           </cell>
         </row>
         <row r="14">
           <cell r="B14">
-            <v>243735.50674831436</v>
+            <v>253109.8297483144</v>
           </cell>
           <cell r="C14">
             <v>572841.76700551296</v>
           </cell>
           <cell r="D14">
-            <v>0.42548487346239311</v>
+            <v>0.44184946756139465</v>
           </cell>
         </row>
         <row r="15">
@@ -401,65 +401,65 @@
         </row>
         <row r="24">
           <cell r="B24">
-            <v>273914.7186931668</v>
+            <v>196969.34364119239</v>
           </cell>
           <cell r="C24">
-            <v>600540.40515975107</v>
+            <v>507836.94488207204</v>
           </cell>
           <cell r="D24">
-            <v>0.45611372080834783</v>
+            <v>0.38785942146633673</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25">
-            <v>326625.68646658427</v>
+            <v>310867.60124087968</v>
           </cell>
           <cell r="D25">
-            <v>0.54388627919165211</v>
+            <v>0.61214057853366333</v>
           </cell>
         </row>
         <row r="29">
           <cell r="B29">
-            <v>19.875583786661061</v>
+            <v>14.292334167443981</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>9.8755837866610605</v>
+            <v>4.2923341674439808</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30">
-            <v>85.206477677853755</v>
+            <v>81.095683601751347</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>70.206477677853755</v>
+            <v>66.095683601751347</v>
           </cell>
         </row>
         <row r="34">
           <cell r="B34">
-            <v>273914.7186931668</v>
+            <v>196969.34364119239</v>
           </cell>
           <cell r="C34">
-            <v>243735.50674831436</v>
+            <v>253109.8297483144</v>
           </cell>
           <cell r="D34">
-            <v>235464.38419412248</v>
+            <v>270563.47762654774</v>
           </cell>
         </row>
         <row r="35">
           <cell r="B35">
-            <v>326625.68646658427</v>
+            <v>310867.60124087968</v>
           </cell>
           <cell r="C35">
             <v>19504.496894714972</v>
           </cell>
           <cell r="D35">
-            <v>115442.23722641317</v>
+            <v>128137.35747940397</v>
           </cell>
         </row>
       </sheetData>
@@ -885,7 +885,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>273914.7186931668</v>
+        <v>196969.34364119239</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -893,7 +893,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>19.875583786661061</v>
+        <v>14.292334167443981</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -902,7 +902,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>326625.68646658427</v>
+        <v>310867.60124087968</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -910,7 +910,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>85.206477677853755</v>
+        <v>81.095683601751347</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -941,7 +941,7 @@
       </c>
       <c r="B14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B14</f>
-        <v>243735.50674831436</v>
+        <v>253109.8297483144</v>
       </c>
       <c r="C14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C14</f>
@@ -949,7 +949,7 @@
       </c>
       <c r="D14" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D14</f>
-        <v>0.42548487346239311</v>
+        <v>0.44184946756139465</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1050,15 +1050,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>273914.7186931668</v>
+        <v>196969.34364119239</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>600540.40515975107</v>
+        <v>507836.94488207204</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.45611372080834783</v>
+        <v>0.38785942146633673</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>326625.68646658427</v>
+        <v>310867.60124087968</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.54388627919165211</v>
+        <v>0.61214057853366333</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>19.875583786661061</v>
+        <v>14.292334167443981</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>9.8755837866610605</v>
+        <v>4.2923341674439808</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>85.206477677853755</v>
+        <v>81.095683601751347</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>70.206477677853755</v>
+        <v>66.095683601751347</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1159,15 +1159,15 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>273914.7186931668</v>
+        <v>196969.34364119239</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
-        <v>243735.50674831436</v>
+        <v>253109.8297483144</v>
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>235464.38419412248</v>
+        <v>270563.47762654774</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>326625.68646658427</v>
+        <v>310867.60124087968</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>115442.23722641317</v>
+        <v>128137.35747940397</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF2044F-D960-4004-B0EE-5709A34AF761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F30803-C71A-4C76-9433-09DC4F758925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -338,24 +338,24 @@
         </row>
         <row r="9">
           <cell r="B9">
-            <v>196969.34364119239</v>
+            <v>184379.72925540741</v>
           </cell>
           <cell r="C9">
             <v>13781.46783678359</v>
           </cell>
           <cell r="D9">
-            <v>14.292334167443981</v>
+            <v>13.378816497563962</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>310867.60124087968</v>
+            <v>310359.41383011488</v>
           </cell>
           <cell r="C10">
             <v>3833.3433721023121</v>
           </cell>
           <cell r="D10">
-            <v>81.095683601751347</v>
+            <v>80.963113320032463</v>
           </cell>
         </row>
         <row r="14">
@@ -371,13 +371,13 @@
         </row>
         <row r="15">
           <cell r="B15">
-            <v>19504.496894714972</v>
+            <v>22129.329197987612</v>
           </cell>
           <cell r="C15">
             <v>88362.038183632205</v>
           </cell>
           <cell r="D15">
-            <v>0.22073389541084509</v>
+            <v>0.25043932499609034</v>
           </cell>
         </row>
         <row r="19">
@@ -401,65 +401,65 @@
         </row>
         <row r="24">
           <cell r="B24">
-            <v>196969.34364119239</v>
+            <v>184379.72925540741</v>
           </cell>
           <cell r="C24">
-            <v>507836.94488207204</v>
+            <v>494739.14308552229</v>
           </cell>
           <cell r="D24">
-            <v>0.38785942146633673</v>
+            <v>0.37268069816649801</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25">
-            <v>310867.60124087968</v>
+            <v>310359.41383011488</v>
           </cell>
           <cell r="D25">
-            <v>0.61214057853366333</v>
+            <v>0.62731930183350193</v>
           </cell>
         </row>
         <row r="29">
           <cell r="B29">
-            <v>14.292334167443981</v>
+            <v>13.378816497563962</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>4.2923341674439808</v>
+            <v>3.3788164975639621</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30">
-            <v>81.095683601751347</v>
+            <v>80.963113320032463</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>66.095683601751347</v>
+            <v>65.963113320032463</v>
           </cell>
         </row>
         <row r="34">
           <cell r="B34">
-            <v>196969.34364119239</v>
+            <v>184379.72925540741</v>
           </cell>
           <cell r="C34">
             <v>253109.8297483144</v>
           </cell>
           <cell r="D34">
-            <v>270563.47762654774</v>
+            <v>277723.5038781222</v>
           </cell>
         </row>
         <row r="35">
           <cell r="B35">
-            <v>310867.60124087968</v>
+            <v>310359.41383011488</v>
           </cell>
           <cell r="C35">
-            <v>19504.496894714972</v>
+            <v>22129.329197987612</v>
           </cell>
           <cell r="D35">
-            <v>128137.35747940397</v>
+            <v>132639.78334740395</v>
           </cell>
         </row>
       </sheetData>
@@ -885,7 +885,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>196969.34364119239</v>
+        <v>184379.72925540741</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -893,7 +893,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>14.292334167443981</v>
+        <v>13.378816497563962</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -902,7 +902,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>310867.60124087968</v>
+        <v>310359.41383011488</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -910,7 +910,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>81.095683601751347</v>
+        <v>80.963113320032463</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -958,7 +958,7 @@
       </c>
       <c r="B15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B15</f>
-        <v>19504.496894714972</v>
+        <v>22129.329197987612</v>
       </c>
       <c r="C15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C15</f>
@@ -966,7 +966,7 @@
       </c>
       <c r="D15" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D15</f>
-        <v>0.22073389541084509</v>
+        <v>0.25043932499609034</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1050,15 +1050,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>196969.34364119239</v>
+        <v>184379.72925540741</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>507836.94488207204</v>
+        <v>494739.14308552229</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.38785942146633673</v>
+        <v>0.37268069816649801</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>310867.60124087968</v>
+        <v>310359.41383011488</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.61214057853366333</v>
+        <v>0.62731930183350193</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>14.292334167443981</v>
+        <v>13.378816497563962</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>4.2923341674439808</v>
+        <v>3.3788164975639621</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>81.095683601751347</v>
+        <v>80.963113320032463</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>66.095683601751347</v>
+        <v>65.963113320032463</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>196969.34364119239</v>
+        <v>184379.72925540741</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>270563.47762654774</v>
+        <v>277723.5038781222</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1176,15 +1176,15 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>310867.60124087968</v>
+        <v>310359.41383011488</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
-        <v>19504.496894714972</v>
+        <v>22129.329197987612</v>
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>128137.35747940397</v>
+        <v>132639.78334740395</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F30803-C71A-4C76-9433-09DC4F758925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E47D0541-F428-4893-8FE3-4F3DED004FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -338,24 +338,24 @@
         </row>
         <row r="9">
           <cell r="B9">
-            <v>184379.72925540741</v>
+            <v>158805.31728305647</v>
           </cell>
           <cell r="C9">
             <v>13781.46783678359</v>
           </cell>
           <cell r="D9">
-            <v>13.378816497563962</v>
+            <v>11.523106186062073</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>310359.41383011488</v>
+            <v>273117.97634472855</v>
           </cell>
           <cell r="C10">
             <v>3833.3433721023121</v>
           </cell>
           <cell r="D10">
-            <v>80.963113320032463</v>
+            <v>71.247981157227528</v>
           </cell>
         </row>
         <row r="14">
@@ -371,13 +371,13 @@
         </row>
         <row r="15">
           <cell r="B15">
-            <v>22129.329197987612</v>
+            <v>65234.433197987615</v>
           </cell>
           <cell r="C15">
             <v>88362.038183632205</v>
           </cell>
           <cell r="D15">
-            <v>0.25043932499609034</v>
+            <v>0.7382631109347968</v>
           </cell>
         </row>
         <row r="19">
@@ -401,65 +401,65 @@
         </row>
         <row r="24">
           <cell r="B24">
-            <v>184379.72925540741</v>
+            <v>158805.31728305647</v>
           </cell>
           <cell r="C24">
-            <v>494739.14308552229</v>
+            <v>431923.29362778505</v>
           </cell>
           <cell r="D24">
-            <v>0.37268069816649801</v>
+            <v>0.36767018502111354</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25">
-            <v>310359.41383011488</v>
+            <v>273117.97634472855</v>
           </cell>
           <cell r="D25">
-            <v>0.62731930183350193</v>
+            <v>0.63232981497888641</v>
           </cell>
         </row>
         <row r="29">
           <cell r="B29">
-            <v>13.378816497563962</v>
+            <v>11.523106186062073</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>3.3788164975639621</v>
+            <v>1.5231061860620727</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30">
-            <v>80.963113320032463</v>
+            <v>71.247981157227528</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>65.963113320032463</v>
+            <v>56.247981157227528</v>
           </cell>
         </row>
         <row r="34">
           <cell r="B34">
-            <v>184379.72925540741</v>
+            <v>158805.31728305647</v>
           </cell>
           <cell r="C34">
             <v>253109.8297483144</v>
           </cell>
           <cell r="D34">
-            <v>277723.5038781222</v>
+            <v>303849.98242812214</v>
           </cell>
         </row>
         <row r="35">
           <cell r="B35">
-            <v>310359.41383011488</v>
+            <v>273117.97634472855</v>
           </cell>
           <cell r="C35">
-            <v>22129.329197987612</v>
+            <v>65234.433197987615</v>
           </cell>
           <cell r="D35">
-            <v>132639.78334740395</v>
+            <v>144119.33500895023</v>
           </cell>
         </row>
       </sheetData>
@@ -885,7 +885,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>184379.72925540741</v>
+        <v>158805.31728305647</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -893,7 +893,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>13.378816497563962</v>
+        <v>11.523106186062073</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -902,7 +902,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>310359.41383011488</v>
+        <v>273117.97634472855</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -910,7 +910,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>80.963113320032463</v>
+        <v>71.247981157227528</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -958,7 +958,7 @@
       </c>
       <c r="B15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B15</f>
-        <v>22129.329197987612</v>
+        <v>65234.433197987615</v>
       </c>
       <c r="C15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C15</f>
@@ -966,7 +966,7 @@
       </c>
       <c r="D15" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D15</f>
-        <v>0.25043932499609034</v>
+        <v>0.7382631109347968</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1050,15 +1050,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>184379.72925540741</v>
+        <v>158805.31728305647</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>494739.14308552229</v>
+        <v>431923.29362778505</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.37268069816649801</v>
+        <v>0.36767018502111354</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>310359.41383011488</v>
+        <v>273117.97634472855</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.62731930183350193</v>
+        <v>0.63232981497888641</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>13.378816497563962</v>
+        <v>11.523106186062073</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>3.3788164975639621</v>
+        <v>1.5231061860620727</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>80.963113320032463</v>
+        <v>71.247981157227528</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>65.963113320032463</v>
+        <v>56.247981157227528</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>184379.72925540741</v>
+        <v>158805.31728305647</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>277723.5038781222</v>
+        <v>303849.98242812214</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1176,15 +1176,15 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>310359.41383011488</v>
+        <v>273117.97634472855</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
-        <v>22129.329197987612</v>
+        <v>65234.433197987615</v>
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>132639.78334740395</v>
+        <v>144119.33500895023</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E47D0541-F428-4893-8FE3-4F3DED004FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0025216-E4AD-49C5-ADE1-F07A9A867C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -338,35 +338,35 @@
         </row>
         <row r="9">
           <cell r="B9">
-            <v>158805.31728305647</v>
+            <v>152796.54664881344</v>
           </cell>
           <cell r="C9">
             <v>13781.46783678359</v>
           </cell>
           <cell r="D9">
-            <v>11.523106186062073</v>
+            <v>11.087102510299376</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>273117.97634472855</v>
+            <v>263629.43836875301</v>
           </cell>
           <cell r="C10">
             <v>3833.3433721023121</v>
           </cell>
           <cell r="D10">
-            <v>71.247981157227528</v>
+            <v>68.772716863131222</v>
           </cell>
         </row>
         <row r="14">
           <cell r="B14">
-            <v>253109.8297483144</v>
+            <v>254675.22690830033</v>
           </cell>
           <cell r="C14">
             <v>572841.76700551296</v>
           </cell>
           <cell r="D14">
-            <v>0.44184946756139465</v>
+            <v>0.44458215440468984</v>
           </cell>
         </row>
         <row r="15">
@@ -401,65 +401,65 @@
         </row>
         <row r="24">
           <cell r="B24">
-            <v>158805.31728305647</v>
+            <v>152796.54664881344</v>
           </cell>
           <cell r="C24">
-            <v>431923.29362778505</v>
+            <v>416425.98501756648</v>
           </cell>
           <cell r="D24">
-            <v>0.36767018502111354</v>
+            <v>0.36692366025709922</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25">
-            <v>273117.97634472855</v>
+            <v>263629.43836875301</v>
           </cell>
           <cell r="D25">
-            <v>0.63232981497888641</v>
+            <v>0.63307633974290078</v>
           </cell>
         </row>
         <row r="29">
           <cell r="B29">
-            <v>11.523106186062073</v>
+            <v>11.087102510299376</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>1.5231061860620727</v>
+            <v>1.0871025102993759</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30">
-            <v>71.247981157227528</v>
+            <v>68.772716863131222</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>56.247981157227528</v>
+            <v>53.772716863131222</v>
           </cell>
         </row>
         <row r="34">
           <cell r="B34">
-            <v>158805.31728305647</v>
+            <v>152796.54664881344</v>
           </cell>
           <cell r="C34">
-            <v>253109.8297483144</v>
+            <v>254675.22690830033</v>
           </cell>
           <cell r="D34">
-            <v>303849.98242812214</v>
+            <v>314256.89941340371</v>
           </cell>
         </row>
         <row r="35">
           <cell r="B35">
-            <v>273117.97634472855</v>
+            <v>263629.43836875301</v>
           </cell>
           <cell r="C35">
             <v>65234.433197987615</v>
           </cell>
           <cell r="D35">
-            <v>144119.33500895023</v>
+            <v>150532.20706519624</v>
           </cell>
         </row>
       </sheetData>
@@ -885,7 +885,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>158805.31728305647</v>
+        <v>152796.54664881344</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -893,7 +893,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>11.523106186062073</v>
+        <v>11.087102510299376</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -902,7 +902,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>273117.97634472855</v>
+        <v>263629.43836875301</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -910,7 +910,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>71.247981157227528</v>
+        <v>68.772716863131222</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -941,7 +941,7 @@
       </c>
       <c r="B14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B14</f>
-        <v>253109.8297483144</v>
+        <v>254675.22690830033</v>
       </c>
       <c r="C14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C14</f>
@@ -949,7 +949,7 @@
       </c>
       <c r="D14" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D14</f>
-        <v>0.44184946756139465</v>
+        <v>0.44458215440468984</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1050,15 +1050,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>158805.31728305647</v>
+        <v>152796.54664881344</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>431923.29362778505</v>
+        <v>416425.98501756648</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.36767018502111354</v>
+        <v>0.36692366025709922</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>273117.97634472855</v>
+        <v>263629.43836875301</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.63232981497888641</v>
+        <v>0.63307633974290078</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>11.523106186062073</v>
+        <v>11.087102510299376</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>1.5231061860620727</v>
+        <v>1.0871025102993759</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>71.247981157227528</v>
+        <v>68.772716863131222</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>56.247981157227528</v>
+        <v>53.772716863131222</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1159,15 +1159,15 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>158805.31728305647</v>
+        <v>152796.54664881344</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
-        <v>253109.8297483144</v>
+        <v>254675.22690830033</v>
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>303849.98242812214</v>
+        <v>314256.89941340371</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>273117.97634472855</v>
+        <v>263629.43836875301</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>144119.33500895023</v>
+        <v>150532.20706519624</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0025216-E4AD-49C5-ADE1-F07A9A867C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE86CB3-3D07-4254-A72E-F798827ABAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -37,122 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="26">
-  <si>
-    <r>
-      <t xml:space="preserve">DASHBOARD - FINANCIERO - KPIs - </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>AGOSTO 2026</t>
-    </r>
-  </si>
-  <si>
-    <t>DIAS DE COBERTURA (INICIO MES)</t>
-  </si>
-  <si>
-    <t>CATEGORIA</t>
-  </si>
-  <si>
-    <t>VALOR INICIAL (USD)</t>
-  </si>
-  <si>
-    <t>CONSUMO DIARIO (USD)</t>
-  </si>
-  <si>
-    <r>
-      <t>DIAS DE COBERTURA (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DIO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">MATERIA PRIMA </t>
-  </si>
-  <si>
-    <t>MATERIAL EMPAQUE</t>
-  </si>
-  <si>
-    <t>DIAS DE COBERTURA (TIEMPO REAL)</t>
-  </si>
-  <si>
-    <t>INVENTARIO DISPONIBLE (USD)</t>
-  </si>
-  <si>
-    <t>SUPPLIER FILL RATE</t>
-  </si>
-  <si>
-    <t>COSTO RECEPCION (USD)</t>
-  </si>
-  <si>
-    <t>COSTO REQUERIMIENTO (USD)</t>
-  </si>
-  <si>
-    <t>FILL RATE</t>
-  </si>
-  <si>
-    <t>ESTRUCTURA DEL CAPITAL INMOVILIZADO (INICIO MES)</t>
-  </si>
-  <si>
-    <t>VALOR INICIAL TOTAL (USD)</t>
-  </si>
-  <si>
-    <t>CAPITAL ALLOCATION</t>
-  </si>
-  <si>
-    <t>ESTRUCTURA DEL CAPITAL INMOVILIZADO (TIEMPO REAL)</t>
-  </si>
-  <si>
-    <t>VALOR TOTAL (USD)</t>
-  </si>
-  <si>
-    <t>VARIABLE DE TIEMPO DE ENTREGA</t>
-  </si>
-  <si>
-    <t>DIO</t>
-  </si>
-  <si>
-    <t>LEAD TIME</t>
-  </si>
-  <si>
-    <t>MARGEN DE SEGURIDAD</t>
-  </si>
-  <si>
-    <t>MOVIMIENTOS (MES ACTUAL)</t>
-  </si>
-  <si>
-    <t>RECEPCION/COMPRAS (USD)</t>
-  </si>
-  <si>
-    <t>CONSUMO (USD)</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -160,7 +45,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$$-2C0A]\ #,##0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,14 +70,6 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -244,7 +121,7 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -253,7 +130,7 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -291,22 +168,22 @@
       <sheetName val="REQUERIMIENTO COMPRAS"/>
       <sheetName val="DASHBOARD FINANCIERO"/>
       <sheetName val="VINCULO VTS BY SKU"/>
+      <sheetName val="FILL RATE"/>
       <sheetName val="MPS"/>
-      <sheetName val="FILL RATE"/>
       <sheetName val="BOM (Recetas)"/>
       <sheetName val="Explosión de materiales"/>
-      <sheetName val="FOTORequerimienMateriaPrima08"/>
+      <sheetName val="FOTORequerimienMateriaPrima09"/>
       <sheetName val="Requerimiento Materia Prima"/>
       <sheetName val="VINCULO MP"/>
       <sheetName val="VALOR $ CONSUMO MP"/>
-      <sheetName val="FOTORequerimienMaterialConten08"/>
+      <sheetName val="FOTORequerimienMaterialConten09"/>
       <sheetName val="Requerimien Material Contenedor"/>
       <sheetName val="VINCULO MC"/>
       <sheetName val="VALOR $ CONSUMO MC"/>
-      <sheetName val="FOTORequerimientoMaterialEmpa08"/>
+      <sheetName val="FOTORequerimientoMaterialEmpa09"/>
       <sheetName val="Requerimiento Material Empaque"/>
+      <sheetName val="VINCULO ME"/>
       <sheetName val="VALOR $ CONSUMO ME"/>
-      <sheetName val="VINCULO ME"/>
       <sheetName val="Plan Producción Semanal"/>
       <sheetName val="Plan Maduraciòn Semanal"/>
       <sheetName val="Panel Producción Diario"/>
@@ -314,152 +191,332 @@
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>DASHBOARD - FINANCIERO - KPIs - SEPTIEMBRE 2026</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>DIAS DE COBERTURA (INICIO MES)</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>CATEGORIA</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v>VALOR INICIAL (USD)</v>
+          </cell>
+          <cell r="C3" t="str">
+            <v>CONSUMO DIARIO (USD)</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v>DIAS DE COBERTURA (DIO)</v>
+          </cell>
+        </row>
         <row r="4">
+          <cell r="A4" t="str">
+            <v xml:space="preserve">MATERIA PRIMA </v>
+          </cell>
           <cell r="B4">
-            <v>150253.06764921901</v>
+            <v>186408.39212143651</v>
           </cell>
           <cell r="C4">
-            <v>13781.46783678359</v>
+            <v>15307</v>
           </cell>
           <cell r="D4">
-            <v>10.902544593122677</v>
+            <v>12.177983414218103</v>
           </cell>
         </row>
         <row r="5">
+          <cell r="A5" t="str">
+            <v>MATERIAL EMPAQUE</v>
+          </cell>
           <cell r="B5">
-            <v>349539.95608949504</v>
+            <v>310223</v>
           </cell>
           <cell r="C5">
-            <v>3833.3433721023121</v>
+            <v>7348</v>
           </cell>
           <cell r="D5">
-            <v>91.184097577409986</v>
+            <v>42.218698965704952</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>DIAS DE COBERTURA (TIEMPO REAL)</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>CATEGORIA</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v>INVENTARIO DISPONIBLE (USD)</v>
+          </cell>
+          <cell r="C8" t="str">
+            <v>CONSUMO DIARIO (USD)</v>
+          </cell>
+          <cell r="D8" t="str">
+            <v>DIAS DE COBERTURA (DIO)</v>
           </cell>
         </row>
         <row r="9">
+          <cell r="A9" t="str">
+            <v xml:space="preserve">MATERIA PRIMA </v>
+          </cell>
           <cell r="B9">
-            <v>152796.54664881344</v>
+            <v>186408.39212143651</v>
           </cell>
           <cell r="C9">
             <v>13781.46783678359</v>
           </cell>
           <cell r="D9">
-            <v>11.087102510299376</v>
+            <v>13.526018732482253</v>
           </cell>
         </row>
         <row r="10">
+          <cell r="A10" t="str">
+            <v>MATERIAL EMPAQUE</v>
+          </cell>
           <cell r="B10">
-            <v>263629.43836875301</v>
+            <v>310222.90694886539</v>
           </cell>
           <cell r="C10">
             <v>3833.3433721023121</v>
           </cell>
           <cell r="D10">
-            <v>68.772716863131222</v>
+            <v>80.927502922528575</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>SUPPLIER FILL RATE</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>CATEGORIA</v>
+          </cell>
+          <cell r="B13" t="str">
+            <v>COSTO RECEPCION (USD)</v>
+          </cell>
+          <cell r="C13" t="str">
+            <v>COSTO REQUERIMIENTO (USD)</v>
+          </cell>
+          <cell r="D13" t="str">
+            <v>FILL RATE</v>
           </cell>
         </row>
         <row r="14">
+          <cell r="A14" t="str">
+            <v xml:space="preserve">MATERIA PRIMA </v>
+          </cell>
           <cell r="B14">
-            <v>254675.22690830033</v>
+            <v>106085.496</v>
           </cell>
           <cell r="C14">
             <v>572841.76700551296</v>
           </cell>
           <cell r="D14">
-            <v>0.44458215440468984</v>
+            <v>0.1851916220329986</v>
           </cell>
         </row>
         <row r="15">
+          <cell r="A15" t="str">
+            <v>MATERIAL EMPAQUE</v>
+          </cell>
           <cell r="B15">
-            <v>65234.433197987615</v>
+            <v>51176.87999999999</v>
           </cell>
           <cell r="C15">
             <v>88362.038183632205</v>
           </cell>
           <cell r="D15">
-            <v>0.7382631109347968</v>
+            <v>0.57917269737084642</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17" t="str">
+            <v>ESTRUCTURA DEL CAPITAL INMOVILIZADO (INICIO MES)</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18" t="str">
+            <v>CATEGORIA</v>
+          </cell>
+          <cell r="B18" t="str">
+            <v>VALOR INICIAL (USD)</v>
+          </cell>
+          <cell r="C18" t="str">
+            <v>VALOR INICIAL TOTAL (USD)</v>
+          </cell>
+          <cell r="D18" t="str">
+            <v>CAPITAL ALLOCATION</v>
           </cell>
         </row>
         <row r="19">
+          <cell r="A19" t="str">
+            <v xml:space="preserve">MATERIA PRIMA </v>
+          </cell>
           <cell r="B19">
-            <v>150253.06764921901</v>
+            <v>186408.39212143651</v>
           </cell>
           <cell r="C19">
-            <v>499793.02373871405</v>
+            <v>496631.39212143654</v>
           </cell>
           <cell r="D19">
-            <v>0.30063058208625487</v>
+            <v>0.37534556832012717</v>
           </cell>
         </row>
         <row r="20">
+          <cell r="A20" t="str">
+            <v>MATERIAL EMPAQUE</v>
+          </cell>
           <cell r="B20">
-            <v>349539.95608949504</v>
+            <v>310223</v>
           </cell>
           <cell r="D20">
-            <v>0.69936941791374507</v>
+            <v>0.62465443167987278</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22" t="str">
+            <v>ESTRUCTURA DEL CAPITAL INMOVILIZADO (TIEMPO REAL)</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23" t="str">
+            <v>CATEGORIA</v>
+          </cell>
+          <cell r="B23" t="str">
+            <v>INVENTARIO DISPONIBLE (USD)</v>
+          </cell>
+          <cell r="C23" t="str">
+            <v>VALOR TOTAL (USD)</v>
+          </cell>
+          <cell r="D23" t="str">
+            <v>CAPITAL ALLOCATION</v>
           </cell>
         </row>
         <row r="24">
+          <cell r="A24" t="str">
+            <v xml:space="preserve">MATERIA PRIMA </v>
+          </cell>
           <cell r="B24">
-            <v>152796.54664881344</v>
+            <v>186408.39212143651</v>
           </cell>
           <cell r="C24">
-            <v>416425.98501756648</v>
+            <v>496631.29907030193</v>
           </cell>
           <cell r="D24">
-            <v>0.36692366025709922</v>
+            <v>0.37534563864660692</v>
           </cell>
         </row>
         <row r="25">
+          <cell r="A25" t="str">
+            <v>MATERIAL EMPAQUE</v>
+          </cell>
           <cell r="B25">
-            <v>263629.43836875301</v>
+            <v>310222.90694886539</v>
           </cell>
           <cell r="D25">
-            <v>0.63307633974290078</v>
+            <v>0.62465436135339303</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27" t="str">
+            <v>VARIABLE DE TIEMPO DE ENTREGA</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28" t="str">
+            <v>CATEGORIA</v>
+          </cell>
+          <cell r="B28" t="str">
+            <v>DIO</v>
+          </cell>
+          <cell r="C28" t="str">
+            <v>LEAD TIME</v>
+          </cell>
+          <cell r="D28" t="str">
+            <v>MARGEN DE SEGURIDAD</v>
           </cell>
         </row>
         <row r="29">
+          <cell r="A29" t="str">
+            <v xml:space="preserve">MATERIA PRIMA </v>
+          </cell>
           <cell r="B29">
-            <v>11.087102510299376</v>
+            <v>13.526018732482253</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>1.0871025102993759</v>
+            <v>3.5260187324822532</v>
           </cell>
         </row>
         <row r="30">
+          <cell r="A30" t="str">
+            <v>MATERIAL EMPAQUE</v>
+          </cell>
           <cell r="B30">
-            <v>68.772716863131222</v>
+            <v>80.927502922528575</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>53.772716863131222</v>
+            <v>65.927502922528575</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32" t="str">
+            <v>MOVIMIENTOS (MES ACTUAL)</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33" t="str">
+            <v>CATEGORIA</v>
+          </cell>
+          <cell r="B33" t="str">
+            <v>INVENTARIO DISPONIBLE (USD)</v>
+          </cell>
+          <cell r="C33" t="str">
+            <v>RECEPCION/COMPRAS (USD)</v>
+          </cell>
+          <cell r="D33" t="str">
+            <v>CONSUMO (USD)</v>
           </cell>
         </row>
         <row r="34">
+          <cell r="A34" t="str">
+            <v xml:space="preserve">MATERIA PRIMA </v>
+          </cell>
           <cell r="B34">
-            <v>152796.54664881344</v>
+            <v>186408.39212143651</v>
           </cell>
           <cell r="C34">
-            <v>254675.22690830033</v>
+            <v>106085.496</v>
           </cell>
           <cell r="D34">
-            <v>314256.89941340371</v>
+            <v>73716.443770643091</v>
           </cell>
         </row>
         <row r="35">
+          <cell r="A35" t="str">
+            <v>MATERIAL EMPAQUE</v>
+          </cell>
           <cell r="B35">
-            <v>263629.43836875301</v>
+            <v>310222.90694886539</v>
           </cell>
           <cell r="C35">
-            <v>65234.433197987615</v>
+            <v>51176.87999999999</v>
           </cell>
           <cell r="D35">
-            <v>150532.20706519624</v>
+            <v>34417.548806354411</v>
           </cell>
         </row>
       </sheetData>
@@ -794,98 +851,112 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
+      <c r="A1" s="10" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A1</f>
+        <v>DASHBOARD - FINANCIERO - KPIs - SEPTIEMBRE 2026</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>1</v>
+      <c r="A2" s="8" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A2</f>
+        <v>DIAS DE COBERTURA (INICIO MES)</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
+      <c r="A3" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A3</f>
+        <v>CATEGORIA</v>
+      </c>
+      <c r="B3" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!B3</f>
+        <v>VALOR INICIAL (USD)</v>
+      </c>
+      <c r="C3" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!C3</f>
+        <v>CONSUMO DIARIO (USD)</v>
+      </c>
+      <c r="D3" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!D3</f>
+        <v>DIAS DE COBERTURA (DIO)</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
+      <c r="A4" s="1" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A4</f>
+        <v xml:space="preserve">MATERIA PRIMA </v>
       </c>
       <c r="B4" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B4</f>
-        <v>150253.06764921901</v>
+        <v>186408.39212143651</v>
       </c>
       <c r="C4" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C4</f>
-        <v>13781.46783678359</v>
+        <v>15307</v>
       </c>
       <c r="D4" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D4</f>
-        <v>10.902544593122677</v>
+        <v>12.177983414218103</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
+      <c r="A5" s="1" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A5</f>
+        <v>MATERIAL EMPAQUE</v>
       </c>
       <c r="B5" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B5</f>
-        <v>349539.95608949504</v>
+        <v>310223</v>
       </c>
       <c r="C5" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C5</f>
-        <v>3833.3433721023121</v>
+        <v>7348</v>
       </c>
       <c r="D5" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D5</f>
-        <v>91.184097577409986</v>
+        <v>42.218698965704952</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>8</v>
+      <c r="A7" s="8" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A7</f>
+        <v>DIAS DE COBERTURA (TIEMPO REAL)</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" t="s">
-        <v>5</v>
+      <c r="A8" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A8</f>
+        <v>CATEGORIA</v>
+      </c>
+      <c r="B8" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!B8</f>
+        <v>INVENTARIO DISPONIBLE (USD)</v>
+      </c>
+      <c r="C8" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!C8</f>
+        <v>CONSUMO DIARIO (USD)</v>
+      </c>
+      <c r="D8" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!D8</f>
+        <v>DIAS DE COBERTURA (DIO)</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
+      <c r="A9" s="1" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A9</f>
+        <v xml:space="preserve">MATERIA PRIMA </v>
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>152796.54664881344</v>
+        <v>186408.39212143651</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -893,16 +964,17 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>11.087102510299376</v>
+        <v>13.526018732482253</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
+      <c r="A10" s="1" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A10</f>
+        <v>MATERIAL EMPAQUE</v>
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>263629.43836875301</v>
+        <v>310222.90694886539</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -910,38 +982,44 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>68.772716863131222</v>
+        <v>80.927502922528575</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>10</v>
+      <c r="A12" s="8" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A12</f>
+        <v>SUPPLIER FILL RATE</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
-        <v>13</v>
+      <c r="A13" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A13</f>
+        <v>CATEGORIA</v>
+      </c>
+      <c r="B13" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!B13</f>
+        <v>COSTO RECEPCION (USD)</v>
+      </c>
+      <c r="C13" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!C13</f>
+        <v>COSTO REQUERIMIENTO (USD)</v>
+      </c>
+      <c r="D13" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!D13</f>
+        <v>FILL RATE</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>6</v>
+      <c r="A14" s="1" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A14</f>
+        <v xml:space="preserve">MATERIA PRIMA </v>
       </c>
       <c r="B14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B14</f>
-        <v>254675.22690830033</v>
+        <v>106085.496</v>
       </c>
       <c r="C14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C14</f>
@@ -949,16 +1027,17 @@
       </c>
       <c r="D14" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D14</f>
-        <v>0.44458215440468984</v>
+        <v>0.1851916220329986</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>7</v>
+      <c r="A15" s="1" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A15</f>
+        <v>MATERIAL EMPAQUE</v>
       </c>
       <c r="B15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B15</f>
-        <v>65234.433197987615</v>
+        <v>51176.87999999999</v>
       </c>
       <c r="C15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C15</f>
@@ -966,144 +1045,164 @@
       </c>
       <c r="D15" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D15</f>
-        <v>0.7382631109347968</v>
+        <v>0.57917269737084642</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>14</v>
+      <c r="A17" s="8" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A17</f>
+        <v>ESTRUCTURA DEL CAPITAL INMOVILIZADO (INICIO MES)</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" t="s">
-        <v>16</v>
+      <c r="A18" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A18</f>
+        <v>CATEGORIA</v>
+      </c>
+      <c r="B18" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!B18</f>
+        <v>VALOR INICIAL (USD)</v>
+      </c>
+      <c r="C18" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!C18</f>
+        <v>VALOR INICIAL TOTAL (USD)</v>
+      </c>
+      <c r="D18" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!D18</f>
+        <v>CAPITAL ALLOCATION</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>6</v>
+      <c r="A19" s="1" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A19</f>
+        <v xml:space="preserve">MATERIA PRIMA </v>
       </c>
       <c r="B19" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B19</f>
-        <v>150253.06764921901</v>
+        <v>186408.39212143651</v>
       </c>
       <c r="C19" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C19</f>
-        <v>499793.02373871405</v>
+        <v>496631.39212143654</v>
       </c>
       <c r="D19" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D19</f>
-        <v>0.30063058208625487</v>
+        <v>0.37534556832012717</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>7</v>
+      <c r="A20" s="1" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A20</f>
+        <v>MATERIAL EMPAQUE</v>
       </c>
       <c r="B20" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B20</f>
-        <v>349539.95608949504</v>
+        <v>310223</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D20</f>
-        <v>0.69936941791374507</v>
+        <v>0.62465443167987278</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
-        <v>17</v>
+      <c r="A22" s="8" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A22</f>
+        <v>ESTRUCTURA DEL CAPITAL INMOVILIZADO (TIEMPO REAL)</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>2</v>
-      </c>
-      <c r="B23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" t="s">
-        <v>16</v>
+      <c r="A23" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A23</f>
+        <v>CATEGORIA</v>
+      </c>
+      <c r="B23" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!B23</f>
+        <v>INVENTARIO DISPONIBLE (USD)</v>
+      </c>
+      <c r="C23" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!C23</f>
+        <v>VALOR TOTAL (USD)</v>
+      </c>
+      <c r="D23" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!D23</f>
+        <v>CAPITAL ALLOCATION</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>6</v>
+      <c r="A24" s="1" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A24</f>
+        <v xml:space="preserve">MATERIA PRIMA </v>
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>152796.54664881344</v>
+        <v>186408.39212143651</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>416425.98501756648</v>
+        <v>496631.29907030193</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.36692366025709922</v>
+        <v>0.37534563864660692</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>7</v>
+      <c r="A25" s="1" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A25</f>
+        <v>MATERIAL EMPAQUE</v>
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>263629.43836875301</v>
+        <v>310222.90694886539</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.63307633974290078</v>
+        <v>0.62465436135339303</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
-        <v>19</v>
+      <c r="A27" s="8" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A27</f>
+        <v>VARIABLE DE TIEMPO DE ENTREGA</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" t="s">
-        <v>22</v>
+      <c r="A28" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A28</f>
+        <v>CATEGORIA</v>
+      </c>
+      <c r="B28" s="5" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!B28</f>
+        <v>DIO</v>
+      </c>
+      <c r="C28" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!C28</f>
+        <v>LEAD TIME</v>
+      </c>
+      <c r="D28" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!D28</f>
+        <v>MARGEN DE SEGURIDAD</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>6</v>
+      <c r="A29" s="1" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A29</f>
+        <v xml:space="preserve">MATERIA PRIMA </v>
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>11.087102510299376</v>
+        <v>13.526018732482253</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1111,16 +1210,17 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>1.0871025102993759</v>
+        <v>3.5260187324822532</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>7</v>
+      <c r="A30" s="1" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A30</f>
+        <v>MATERIAL EMPAQUE</v>
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>68.772716863131222</v>
+        <v>80.927502922528575</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1128,63 +1228,70 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>53.772716863131222</v>
+        <v>65.927502922528575</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
-        <v>23</v>
+      <c r="A32" s="8" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A32</f>
+        <v>MOVIMIENTOS (MES ACTUAL)</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>2</v>
-      </c>
-      <c r="B33" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" t="s">
-        <v>24</v>
-      </c>
-      <c r="D33" t="s">
-        <v>25</v>
+      <c r="A33" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A33</f>
+        <v>CATEGORIA</v>
+      </c>
+      <c r="B33" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!B33</f>
+        <v>INVENTARIO DISPONIBLE (USD)</v>
+      </c>
+      <c r="C33" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!C33</f>
+        <v>RECEPCION/COMPRAS (USD)</v>
+      </c>
+      <c r="D33" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!D33</f>
+        <v>CONSUMO (USD)</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>6</v>
+      <c r="A34" s="1" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A34</f>
+        <v xml:space="preserve">MATERIA PRIMA </v>
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>152796.54664881344</v>
+        <v>186408.39212143651</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
-        <v>254675.22690830033</v>
+        <v>106085.496</v>
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>314256.89941340371</v>
+        <v>73716.443770643091</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>7</v>
+      <c r="A35" s="1" t="str">
+        <f>'[1]DASHBOARD FINANCIERO'!A35</f>
+        <v>MATERIAL EMPAQUE</v>
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>263629.43836875301</v>
+        <v>310222.90694886539</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
-        <v>65234.433197987615</v>
+        <v>51176.87999999999</v>
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>150532.20706519624</v>
+        <v>34417.548806354411</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE86CB3-3D07-4254-A72E-F798827ABAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F24F392-31AD-46FE-83F2-581FD5C70584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -34,10 +34,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -220,13 +216,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B4">
-            <v>186408.39212143651</v>
+            <v>80323.392121437006</v>
           </cell>
           <cell r="C4">
             <v>15307</v>
           </cell>
           <cell r="D4">
-            <v>12.177983414218103</v>
+            <v>5.2474940956057363</v>
           </cell>
         </row>
         <row r="5">
@@ -234,13 +230,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B5">
-            <v>310223</v>
+            <v>258446</v>
           </cell>
           <cell r="C5">
             <v>7348</v>
           </cell>
           <cell r="D5">
-            <v>42.218698965704952</v>
+            <v>35.172291780076215</v>
           </cell>
         </row>
         <row r="7">
@@ -361,13 +357,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B19">
-            <v>186408.39212143651</v>
+            <v>80323.392121437006</v>
           </cell>
           <cell r="C19">
-            <v>496631.39212143654</v>
+            <v>338769.39212143701</v>
           </cell>
           <cell r="D19">
-            <v>0.37534556832012717</v>
+            <v>0.23710345146129339</v>
           </cell>
         </row>
         <row r="20">
@@ -375,10 +371,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B20">
-            <v>310223</v>
+            <v>258446</v>
           </cell>
           <cell r="D20">
-            <v>0.62465443167987278</v>
+            <v>0.76289654853870659</v>
           </cell>
         </row>
         <row r="22">
@@ -893,7 +889,7 @@
       </c>
       <c r="B4" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B4</f>
-        <v>186408.39212143651</v>
+        <v>80323.392121437006</v>
       </c>
       <c r="C4" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C4</f>
@@ -901,7 +897,7 @@
       </c>
       <c r="D4" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D4</f>
-        <v>12.177983414218103</v>
+        <v>5.2474940956057363</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -911,7 +907,7 @@
       </c>
       <c r="B5" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B5</f>
-        <v>310223</v>
+        <v>258446</v>
       </c>
       <c r="C5" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C5</f>
@@ -919,7 +915,7 @@
       </c>
       <c r="D5" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D5</f>
-        <v>42.218698965704952</v>
+        <v>35.172291780076215</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1082,15 +1078,15 @@
       </c>
       <c r="B19" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B19</f>
-        <v>186408.39212143651</v>
+        <v>80323.392121437006</v>
       </c>
       <c r="C19" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C19</f>
-        <v>496631.39212143654</v>
+        <v>338769.39212143701</v>
       </c>
       <c r="D19" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D19</f>
-        <v>0.37534556832012717</v>
+        <v>0.23710345146129339</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1100,12 +1096,12 @@
       </c>
       <c r="B20" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B20</f>
-        <v>310223</v>
+        <v>258446</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D20</f>
-        <v>0.62465443167987278</v>
+        <v>0.76289654853870659</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F24F392-31AD-46FE-83F2-581FD5C70584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C3C089-DDE3-4C7C-A517-09A80AB6653C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -216,13 +216,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B4">
-            <v>80323.392121437006</v>
+            <v>154039.39212143701</v>
           </cell>
           <cell r="C4">
             <v>15307</v>
           </cell>
           <cell r="D4">
-            <v>5.2474940956057363</v>
+            <v>10.063329987681257</v>
           </cell>
         </row>
         <row r="5">
@@ -230,13 +230,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B5">
-            <v>258446</v>
+            <v>292864</v>
           </cell>
           <cell r="C5">
             <v>7348</v>
           </cell>
           <cell r="D5">
-            <v>35.172291780076215</v>
+            <v>39.856287425149702</v>
           </cell>
         </row>
         <row r="7">
@@ -889,7 +889,7 @@
       </c>
       <c r="B4" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B4</f>
-        <v>80323.392121437006</v>
+        <v>154039.39212143701</v>
       </c>
       <c r="C4" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C4</f>
@@ -897,7 +897,7 @@
       </c>
       <c r="D4" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D4</f>
-        <v>5.2474940956057363</v>
+        <v>10.063329987681257</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -907,7 +907,7 @@
       </c>
       <c r="B5" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B5</f>
-        <v>258446</v>
+        <v>292864</v>
       </c>
       <c r="C5" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C5</f>
@@ -915,7 +915,7 @@
       </c>
       <c r="D5" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D5</f>
-        <v>35.172291780076215</v>
+        <v>39.856287425149702</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C3C089-DDE3-4C7C-A517-09A80AB6653C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9953DCE4-C331-4A6B-BA78-8A5EB6F3528B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9953DCE4-C331-4A6B-BA78-8A5EB6F3528B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7038A72F-48D7-4494-B877-6E47FFB849CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -357,13 +357,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B19">
-            <v>80323.392121437006</v>
+            <v>154039.39212143701</v>
           </cell>
           <cell r="C19">
-            <v>338769.39212143701</v>
+            <v>446903.39212143701</v>
           </cell>
           <cell r="D19">
-            <v>0.23710345146129339</v>
+            <v>0.34468163553249537</v>
           </cell>
         </row>
         <row r="20">
@@ -371,10 +371,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B20">
-            <v>258446</v>
+            <v>292864</v>
           </cell>
           <cell r="D20">
-            <v>0.76289654853870659</v>
+            <v>0.65531836446750469</v>
           </cell>
         </row>
         <row r="22">
@@ -1078,15 +1078,15 @@
       </c>
       <c r="B19" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B19</f>
-        <v>80323.392121437006</v>
+        <v>154039.39212143701</v>
       </c>
       <c r="C19" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C19</f>
-        <v>338769.39212143701</v>
+        <v>446903.39212143701</v>
       </c>
       <c r="D19" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D19</f>
-        <v>0.23710345146129339</v>
+        <v>0.34468163553249537</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B20" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B20</f>
-        <v>258446</v>
+        <v>292864</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D20</f>
-        <v>0.76289654853870659</v>
+        <v>0.65531836446750469</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7038A72F-48D7-4494-B877-6E47FFB849CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64010CF3-D02F-485F-92B2-963179F96EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64010CF3-D02F-485F-92B2-963179F96EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332059B0-3861-4FA5-8571-46708A4D9B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -263,13 +263,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B9">
-            <v>186408.39212143651</v>
+            <v>173517.12943427861</v>
           </cell>
           <cell r="C9">
             <v>13781.46783678359</v>
           </cell>
           <cell r="D9">
-            <v>13.526018732482253</v>
+            <v>12.590613096462096</v>
           </cell>
         </row>
         <row r="10">
@@ -277,13 +277,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B10">
-            <v>310222.90694886539</v>
+            <v>278363.73397161684</v>
           </cell>
           <cell r="C10">
             <v>3833.3433721023121</v>
           </cell>
           <cell r="D10">
-            <v>80.927502922528575</v>
+            <v>72.616436084867203</v>
           </cell>
         </row>
         <row r="12">
@@ -310,13 +310,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B14">
-            <v>106085.496</v>
+            <v>107770.872</v>
           </cell>
           <cell r="C14">
             <v>572841.76700551296</v>
           </cell>
           <cell r="D14">
-            <v>0.1851916220329986</v>
+            <v>0.18813375386952683</v>
           </cell>
         </row>
         <row r="15">
@@ -357,13 +357,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B19">
-            <v>154039.39212143701</v>
+            <v>80323.392121437006</v>
           </cell>
           <cell r="C19">
-            <v>446903.39212143701</v>
+            <v>338769.39212143701</v>
           </cell>
           <cell r="D19">
-            <v>0.34468163553249537</v>
+            <v>0.23710345146129339</v>
           </cell>
         </row>
         <row r="20">
@@ -371,10 +371,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B20">
-            <v>292864</v>
+            <v>258446</v>
           </cell>
           <cell r="D20">
-            <v>0.65531836446750469</v>
+            <v>0.76289654853870659</v>
           </cell>
         </row>
         <row r="22">
@@ -401,13 +401,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B24">
-            <v>186408.39212143651</v>
+            <v>173517.12943427861</v>
           </cell>
           <cell r="C24">
-            <v>496631.29907030193</v>
+            <v>451880.86340589542</v>
           </cell>
           <cell r="D24">
-            <v>0.37534563864660692</v>
+            <v>0.38398866490263245</v>
           </cell>
         </row>
         <row r="25">
@@ -415,10 +415,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B25">
-            <v>310222.90694886539</v>
+            <v>278363.73397161684</v>
           </cell>
           <cell r="D25">
-            <v>0.62465436135339303</v>
+            <v>0.61601133509736761</v>
           </cell>
         </row>
         <row r="27">
@@ -445,13 +445,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B29">
-            <v>13.526018732482253</v>
+            <v>12.590613096462096</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>3.5260187324822532</v>
+            <v>2.5906130964620964</v>
           </cell>
         </row>
         <row r="30">
@@ -459,13 +459,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B30">
-            <v>80.927502922528575</v>
+            <v>72.616436084867203</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>65.927502922528575</v>
+            <v>57.616436084867203</v>
           </cell>
         </row>
         <row r="32">
@@ -492,13 +492,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B34">
-            <v>186408.39212143651</v>
+            <v>173517.12943427861</v>
           </cell>
           <cell r="C34">
-            <v>106085.496</v>
+            <v>107770.872</v>
           </cell>
           <cell r="D34">
-            <v>73716.443770643091</v>
+            <v>88672.067144643079</v>
           </cell>
         </row>
         <row r="35">
@@ -506,13 +506,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B35">
-            <v>310222.90694886539</v>
+            <v>278363.73397161684</v>
           </cell>
           <cell r="C35">
             <v>51176.87999999999</v>
           </cell>
           <cell r="D35">
-            <v>34417.548806354411</v>
+            <v>42576.322517884662</v>
           </cell>
         </row>
       </sheetData>
@@ -952,7 +952,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>186408.39212143651</v>
+        <v>173517.12943427861</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -960,7 +960,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>13.526018732482253</v>
+        <v>12.590613096462096</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>310222.90694886539</v>
+        <v>278363.73397161684</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -978,7 +978,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>80.927502922528575</v>
+        <v>72.616436084867203</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B14</f>
-        <v>106085.496</v>
+        <v>107770.872</v>
       </c>
       <c r="C14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C14</f>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D14" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D14</f>
-        <v>0.1851916220329986</v>
+        <v>0.18813375386952683</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1078,15 +1078,15 @@
       </c>
       <c r="B19" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B19</f>
-        <v>154039.39212143701</v>
+        <v>80323.392121437006</v>
       </c>
       <c r="C19" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C19</f>
-        <v>446903.39212143701</v>
+        <v>338769.39212143701</v>
       </c>
       <c r="D19" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D19</f>
-        <v>0.34468163553249537</v>
+        <v>0.23710345146129339</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B20" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B20</f>
-        <v>292864</v>
+        <v>258446</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D20</f>
-        <v>0.65531836446750469</v>
+        <v>0.76289654853870659</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1138,15 +1138,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>186408.39212143651</v>
+        <v>173517.12943427861</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>496631.29907030193</v>
+        <v>451880.86340589542</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.37534563864660692</v>
+        <v>0.38398866490263245</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>310222.90694886539</v>
+        <v>278363.73397161684</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.62465436135339303</v>
+        <v>0.61601133509736761</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>13.526018732482253</v>
+        <v>12.590613096462096</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>3.5260187324822532</v>
+        <v>2.5906130964620964</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>80.927502922528575</v>
+        <v>72.616436084867203</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>65.927502922528575</v>
+        <v>57.616436084867203</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1261,15 +1261,15 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>186408.39212143651</v>
+        <v>173517.12943427861</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
-        <v>106085.496</v>
+        <v>107770.872</v>
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>73716.443770643091</v>
+        <v>88672.067144643079</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>310222.90694886539</v>
+        <v>278363.73397161684</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>34417.548806354411</v>
+        <v>42576.322517884662</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332059B0-3861-4FA5-8571-46708A4D9B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F315F40-4877-4538-8669-332762AA889C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -313,10 +313,10 @@
             <v>107770.872</v>
           </cell>
           <cell r="C14">
-            <v>572841.76700551296</v>
+            <v>197224.51117292957</v>
           </cell>
           <cell r="D14">
-            <v>0.18813375386952683</v>
+            <v>0.54643751610318247</v>
           </cell>
         </row>
         <row r="15">
@@ -327,10 +327,10 @@
             <v>51176.87999999999</v>
           </cell>
           <cell r="C15">
-            <v>88362.038183632205</v>
+            <v>47737.609121113812</v>
           </cell>
           <cell r="D15">
-            <v>0.57917269737084642</v>
+            <v>1.072045310651409</v>
           </cell>
         </row>
         <row r="17">
@@ -357,13 +357,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B19">
-            <v>80323.392121437006</v>
+            <v>154039.39212143701</v>
           </cell>
           <cell r="C19">
-            <v>338769.39212143701</v>
+            <v>446903.39212143701</v>
           </cell>
           <cell r="D19">
-            <v>0.23710345146129339</v>
+            <v>0.34468163553249537</v>
           </cell>
         </row>
         <row r="20">
@@ -371,10 +371,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B20">
-            <v>258446</v>
+            <v>292864</v>
           </cell>
           <cell r="D20">
-            <v>0.76289654853870659</v>
+            <v>0.65531836446750469</v>
           </cell>
         </row>
         <row r="22">
@@ -1019,11 +1019,11 @@
       </c>
       <c r="C14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C14</f>
-        <v>572841.76700551296</v>
+        <v>197224.51117292957</v>
       </c>
       <c r="D14" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D14</f>
-        <v>0.18813375386952683</v>
+        <v>0.54643751610318247</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1037,11 +1037,11 @@
       </c>
       <c r="C15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C15</f>
-        <v>88362.038183632205</v>
+        <v>47737.609121113812</v>
       </c>
       <c r="D15" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D15</f>
-        <v>0.57917269737084642</v>
+        <v>1.072045310651409</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1078,15 +1078,15 @@
       </c>
       <c r="B19" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B19</f>
-        <v>80323.392121437006</v>
+        <v>154039.39212143701</v>
       </c>
       <c r="C19" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C19</f>
-        <v>338769.39212143701</v>
+        <v>446903.39212143701</v>
       </c>
       <c r="D19" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D19</f>
-        <v>0.23710345146129339</v>
+        <v>0.34468163553249537</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B20" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B20</f>
-        <v>258446</v>
+        <v>292864</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D20</f>
-        <v>0.76289654853870659</v>
+        <v>0.65531836446750469</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F315F40-4877-4538-8669-332762AA889C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD02A8C6-09F8-4692-9EF0-1818231DFD9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -230,13 +230,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B5">
-            <v>292864</v>
+            <v>269763</v>
           </cell>
           <cell r="C5">
             <v>7348</v>
           </cell>
           <cell r="D5">
-            <v>39.856287425149702</v>
+            <v>36.712438758845941</v>
           </cell>
         </row>
         <row r="7">
@@ -360,10 +360,10 @@
             <v>154039.39212143701</v>
           </cell>
           <cell r="C19">
-            <v>446903.39212143701</v>
+            <v>423802.39212143701</v>
           </cell>
           <cell r="D19">
-            <v>0.34468163553249537</v>
+            <v>0.36346985053661124</v>
           </cell>
         </row>
         <row r="20">
@@ -371,10 +371,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B20">
-            <v>292864</v>
+            <v>269763</v>
           </cell>
           <cell r="D20">
-            <v>0.65531836446750469</v>
+            <v>0.63653014946338882</v>
           </cell>
         </row>
         <row r="22">
@@ -907,7 +907,7 @@
       </c>
       <c r="B5" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B5</f>
-        <v>292864</v>
+        <v>269763</v>
       </c>
       <c r="C5" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C5</f>
@@ -915,7 +915,7 @@
       </c>
       <c r="D5" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D5</f>
-        <v>39.856287425149702</v>
+        <v>36.712438758845941</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1082,11 +1082,11 @@
       </c>
       <c r="C19" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C19</f>
-        <v>446903.39212143701</v>
+        <v>423802.39212143701</v>
       </c>
       <c r="D19" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D19</f>
-        <v>0.34468163553249537</v>
+        <v>0.36346985053661124</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B20" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B20</f>
-        <v>292864</v>
+        <v>269763</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D20</f>
-        <v>0.65531836446750469</v>
+        <v>0.63653014946338882</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD02A8C6-09F8-4692-9EF0-1818231DFD9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8BC7FC-C6FF-49F5-ABFA-29D38F96EE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -263,13 +263,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B9">
-            <v>173517.12943427861</v>
+            <v>177521.71864408237</v>
           </cell>
           <cell r="C9">
             <v>13781.46783678359</v>
           </cell>
           <cell r="D9">
-            <v>12.590613096462096</v>
+            <v>12.88119094036311</v>
           </cell>
         </row>
         <row r="10">
@@ -277,13 +277,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B10">
-            <v>278363.73397161684</v>
+            <v>274869.81610848685</v>
           </cell>
           <cell r="C10">
             <v>3833.3433721023121</v>
           </cell>
           <cell r="D10">
-            <v>72.616436084867203</v>
+            <v>71.704981637932576</v>
           </cell>
         </row>
         <row r="12">
@@ -401,13 +401,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B24">
-            <v>173517.12943427861</v>
+            <v>177521.71864408237</v>
           </cell>
           <cell r="C24">
-            <v>451880.86340589542</v>
+            <v>452391.53475256922</v>
           </cell>
           <cell r="D24">
-            <v>0.38398866490263245</v>
+            <v>0.39240725125675929</v>
           </cell>
         </row>
         <row r="25">
@@ -415,10 +415,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B25">
-            <v>278363.73397161684</v>
+            <v>274869.81610848685</v>
           </cell>
           <cell r="D25">
-            <v>0.61601133509736761</v>
+            <v>0.60759274874324076</v>
           </cell>
         </row>
         <row r="27">
@@ -445,13 +445,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B29">
-            <v>12.590613096462096</v>
+            <v>12.88119094036311</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>2.5906130964620964</v>
+            <v>2.8811909403631102</v>
           </cell>
         </row>
         <row r="30">
@@ -459,13 +459,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B30">
-            <v>72.616436084867203</v>
+            <v>71.704981637932576</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>57.616436084867203</v>
+            <v>56.704981637932576</v>
           </cell>
         </row>
         <row r="32">
@@ -492,13 +492,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B34">
-            <v>173517.12943427861</v>
+            <v>177521.71864408237</v>
           </cell>
           <cell r="C34">
             <v>107770.872</v>
           </cell>
           <cell r="D34">
-            <v>88672.067144643079</v>
+            <v>104980.85059010248</v>
           </cell>
         </row>
         <row r="35">
@@ -506,13 +506,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B35">
-            <v>278363.73397161684</v>
+            <v>274869.81610848685</v>
           </cell>
           <cell r="C35">
             <v>51176.87999999999</v>
           </cell>
           <cell r="D35">
-            <v>42576.322517884662</v>
+            <v>50555.044629929565</v>
           </cell>
         </row>
       </sheetData>
@@ -952,7 +952,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>173517.12943427861</v>
+        <v>177521.71864408237</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -960,7 +960,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>12.590613096462096</v>
+        <v>12.88119094036311</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>278363.73397161684</v>
+        <v>274869.81610848685</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -978,7 +978,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>72.616436084867203</v>
+        <v>71.704981637932576</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1138,15 +1138,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>173517.12943427861</v>
+        <v>177521.71864408237</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>451880.86340589542</v>
+        <v>452391.53475256922</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.38398866490263245</v>
+        <v>0.39240725125675929</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>278363.73397161684</v>
+        <v>274869.81610848685</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.61601133509736761</v>
+        <v>0.60759274874324076</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>12.590613096462096</v>
+        <v>12.88119094036311</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>2.5906130964620964</v>
+        <v>2.8811909403631102</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>72.616436084867203</v>
+        <v>71.704981637932576</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>57.616436084867203</v>
+        <v>56.704981637932576</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>173517.12943427861</v>
+        <v>177521.71864408237</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>88672.067144643079</v>
+        <v>104980.85059010248</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>278363.73397161684</v>
+        <v>274869.81610848685</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>42576.322517884662</v>
+        <v>50555.044629929565</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8BC7FC-C6FF-49F5-ABFA-29D38F96EE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B808096-729A-4A9E-BD71-6F2A6F1EDAF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -277,13 +277,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B10">
-            <v>274869.81610848685</v>
+            <v>274740.64953622804</v>
           </cell>
           <cell r="C10">
             <v>3833.3433721023121</v>
           </cell>
           <cell r="D10">
-            <v>71.704981637932576</v>
+            <v>71.671286098628997</v>
           </cell>
         </row>
         <row r="12">
@@ -313,10 +313,10 @@
             <v>107770.872</v>
           </cell>
           <cell r="C14">
-            <v>197224.51117292957</v>
+            <v>344799.25199999998</v>
           </cell>
           <cell r="D14">
-            <v>0.54643751610318247</v>
+            <v>0.31256121170471685</v>
           </cell>
         </row>
         <row r="15">
@@ -327,10 +327,10 @@
             <v>51176.87999999999</v>
           </cell>
           <cell r="C15">
-            <v>47737.609121113812</v>
+            <v>108924.24443806437</v>
           </cell>
           <cell r="D15">
-            <v>1.072045310651409</v>
+            <v>0.469839201217501</v>
           </cell>
         </row>
         <row r="17">
@@ -404,10 +404,10 @@
             <v>177521.71864408237</v>
           </cell>
           <cell r="C24">
-            <v>452391.53475256922</v>
+            <v>452262.36818031041</v>
           </cell>
           <cell r="D24">
-            <v>0.39240725125675929</v>
+            <v>0.39251932314940485</v>
           </cell>
         </row>
         <row r="25">
@@ -415,10 +415,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B25">
-            <v>274869.81610848685</v>
+            <v>274740.64953622804</v>
           </cell>
           <cell r="D25">
-            <v>0.60759274874324076</v>
+            <v>0.60748067685059515</v>
           </cell>
         </row>
         <row r="27">
@@ -459,13 +459,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B30">
-            <v>71.704981637932576</v>
+            <v>71.671286098628997</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>56.704981637932576</v>
+            <v>56.671286098628997</v>
           </cell>
         </row>
         <row r="32">
@@ -506,13 +506,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B35">
-            <v>274869.81610848685</v>
+            <v>274740.64953622804</v>
           </cell>
           <cell r="C35">
             <v>51176.87999999999</v>
           </cell>
           <cell r="D35">
-            <v>50555.044629929565</v>
+            <v>51261.59342192956</v>
           </cell>
         </row>
       </sheetData>
@@ -970,7 +970,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>274869.81610848685</v>
+        <v>274740.64953622804</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -978,7 +978,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>71.704981637932576</v>
+        <v>71.671286098628997</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1019,11 +1019,11 @@
       </c>
       <c r="C14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C14</f>
-        <v>197224.51117292957</v>
+        <v>344799.25199999998</v>
       </c>
       <c r="D14" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D14</f>
-        <v>0.54643751610318247</v>
+        <v>0.31256121170471685</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1037,11 +1037,11 @@
       </c>
       <c r="C15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C15</f>
-        <v>47737.609121113812</v>
+        <v>108924.24443806437</v>
       </c>
       <c r="D15" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D15</f>
-        <v>1.072045310651409</v>
+        <v>0.469839201217501</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1142,11 +1142,11 @@
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>452391.53475256922</v>
+        <v>452262.36818031041</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.39240725125675929</v>
+        <v>0.39251932314940485</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>274869.81610848685</v>
+        <v>274740.64953622804</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.60759274874324076</v>
+        <v>0.60748067685059515</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>71.704981637932576</v>
+        <v>71.671286098628997</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>56.704981637932576</v>
+        <v>56.671286098628997</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>274869.81610848685</v>
+        <v>274740.64953622804</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>50555.044629929565</v>
+        <v>51261.59342192956</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B808096-729A-4A9E-BD71-6F2A6F1EDAF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75DD9270-A85D-4476-9539-A796C2FBCEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -263,13 +263,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B9">
-            <v>177521.71864408237</v>
+            <v>150320.02510286708</v>
           </cell>
           <cell r="C9">
             <v>13781.46783678359</v>
           </cell>
           <cell r="D9">
-            <v>12.88119094036311</v>
+            <v>10.907403107066262</v>
           </cell>
         </row>
         <row r="10">
@@ -277,13 +277,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B10">
-            <v>274740.64953622804</v>
+            <v>295894.57453017333</v>
           </cell>
           <cell r="C10">
             <v>3833.3433721023121</v>
           </cell>
           <cell r="D10">
-            <v>71.671286098628997</v>
+            <v>77.18968686280158</v>
           </cell>
         </row>
         <row r="12">
@@ -310,13 +310,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B14">
-            <v>107770.872</v>
+            <v>119904.35650000001</v>
           </cell>
           <cell r="C14">
             <v>344799.25199999998</v>
           </cell>
           <cell r="D14">
-            <v>0.31256121170471685</v>
+            <v>0.34775120828858413</v>
           </cell>
         </row>
         <row r="15">
@@ -324,13 +324,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B15">
-            <v>51176.87999999999</v>
+            <v>81503.28</v>
           </cell>
           <cell r="C15">
             <v>108924.24443806437</v>
           </cell>
           <cell r="D15">
-            <v>0.469839201217501</v>
+            <v>0.74825655592537743</v>
           </cell>
         </row>
         <row r="17">
@@ -401,13 +401,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B24">
-            <v>177521.71864408237</v>
+            <v>150320.02510286708</v>
           </cell>
           <cell r="C24">
-            <v>452262.36818031041</v>
+            <v>446214.59963304037</v>
           </cell>
           <cell r="D24">
-            <v>0.39251932314940485</v>
+            <v>0.33687832093904552</v>
           </cell>
         </row>
         <row r="25">
@@ -415,10 +415,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B25">
-            <v>274740.64953622804</v>
+            <v>295894.57453017333</v>
           </cell>
           <cell r="D25">
-            <v>0.60748067685059515</v>
+            <v>0.66312167906095454</v>
           </cell>
         </row>
         <row r="27">
@@ -445,13 +445,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B29">
-            <v>12.88119094036311</v>
+            <v>10.907403107066262</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>2.8811909403631102</v>
+            <v>0.90740310706626204</v>
           </cell>
         </row>
         <row r="30">
@@ -459,13 +459,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B30">
-            <v>71.671286098628997</v>
+            <v>77.18968686280158</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>56.671286098628997</v>
+            <v>62.18968686280158</v>
           </cell>
         </row>
         <row r="32">
@@ -492,13 +492,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B34">
-            <v>177521.71864408237</v>
+            <v>150320.02510286708</v>
           </cell>
           <cell r="C34">
-            <v>107770.872</v>
+            <v>119904.35650000001</v>
           </cell>
           <cell r="D34">
-            <v>104980.85059010248</v>
+            <v>123942.66483131783</v>
           </cell>
         </row>
         <row r="35">
@@ -506,13 +506,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B35">
-            <v>274740.64953622804</v>
+            <v>295894.57453017333</v>
           </cell>
           <cell r="C35">
-            <v>51176.87999999999</v>
+            <v>81503.28</v>
           </cell>
           <cell r="D35">
-            <v>51261.59342192956</v>
+            <v>60700.217828077599</v>
           </cell>
         </row>
       </sheetData>
@@ -952,7 +952,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>177521.71864408237</v>
+        <v>150320.02510286708</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -960,7 +960,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>12.88119094036311</v>
+        <v>10.907403107066262</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>274740.64953622804</v>
+        <v>295894.57453017333</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -978,7 +978,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>71.671286098628997</v>
+        <v>77.18968686280158</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B14</f>
-        <v>107770.872</v>
+        <v>119904.35650000001</v>
       </c>
       <c r="C14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C14</f>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D14" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D14</f>
-        <v>0.31256121170471685</v>
+        <v>0.34775120828858413</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B15</f>
-        <v>51176.87999999999</v>
+        <v>81503.28</v>
       </c>
       <c r="C15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C15</f>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="D15" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D15</f>
-        <v>0.469839201217501</v>
+        <v>0.74825655592537743</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1138,15 +1138,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>177521.71864408237</v>
+        <v>150320.02510286708</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>452262.36818031041</v>
+        <v>446214.59963304037</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.39251932314940485</v>
+        <v>0.33687832093904552</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>274740.64953622804</v>
+        <v>295894.57453017333</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.60748067685059515</v>
+        <v>0.66312167906095454</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>12.88119094036311</v>
+        <v>10.907403107066262</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>2.8811909403631102</v>
+        <v>0.90740310706626204</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>71.671286098628997</v>
+        <v>77.18968686280158</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>56.671286098628997</v>
+        <v>62.18968686280158</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1261,15 +1261,15 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>177521.71864408237</v>
+        <v>150320.02510286708</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
-        <v>107770.872</v>
+        <v>119904.35650000001</v>
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>104980.85059010248</v>
+        <v>123942.66483131783</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1279,15 +1279,15 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>274740.64953622804</v>
+        <v>295894.57453017333</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
-        <v>51176.87999999999</v>
+        <v>81503.28</v>
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>51261.59342192956</v>
+        <v>60700.217828077599</v>
       </c>
     </row>
   </sheetData>
